--- a/Текст и прочее/тестовые данные БД.xlsx
+++ b/Текст и прочее/тестовые данные БД.xlsx
@@ -5,34 +5,42 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SlavanST\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Me\Repos\ClientServer\Текст и прочее\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1A1AD7-0E64-411E-BEE5-70505C8C53C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA8C1A0-6B36-4D10-8EFD-B9CAA7860649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roles" sheetId="1" r:id="rId1"/>
     <sheet name="Users" sheetId="2" r:id="rId2"/>
     <sheet name="Rooms" sheetId="3" r:id="rId3"/>
     <sheet name="Statuses" sheetId="4" r:id="rId4"/>
-    <sheet name="PurityRaidLogs" sheetId="5" r:id="rId5"/>
-    <sheet name="AttendanceLog" sheetId="6" r:id="rId6"/>
-    <sheet name="DutySchedule" sheetId="8" r:id="rId7"/>
-    <sheet name="Students" sheetId="7" r:id="rId8"/>
+    <sheet name="Students" sheetId="7" r:id="rId5"/>
+    <sheet name="Group" sheetId="10" r:id="rId6"/>
+    <sheet name="Лист1" sheetId="9" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="473">
   <si>
     <t>Admin</t>
   </si>
@@ -142,18 +150,6 @@
     <t>RoomId</t>
   </si>
   <si>
-    <t>Marker</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>StudentId</t>
-  </si>
-  <si>
     <t>Phone</t>
   </si>
   <si>
@@ -184,17 +180,1292 @@
     <t>Детский дом</t>
   </si>
   <si>
-    <t>Журналы проверок чистоты</t>
-  </si>
-  <si>
-    <t>График дежурств</t>
+    <t>DateBirthday</t>
+  </si>
+  <si>
+    <t>Смирнов</t>
+  </si>
+  <si>
+    <t>Иван</t>
+  </si>
+  <si>
+    <t>Иванович</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>ул. Ленина</t>
+  </si>
+  <si>
+    <t>Смирнова</t>
+  </si>
+  <si>
+    <t>Мария</t>
+  </si>
+  <si>
+    <t>Ивановна</t>
+  </si>
+  <si>
+    <t>Иванова</t>
+  </si>
+  <si>
+    <t>Петровна</t>
+  </si>
+  <si>
+    <t>ж</t>
+  </si>
+  <si>
+    <t>ул. Пушкина</t>
+  </si>
+  <si>
+    <t>Иванов</t>
+  </si>
+  <si>
+    <t>Петр</t>
+  </si>
+  <si>
+    <t>Маркович</t>
+  </si>
+  <si>
+    <t>Петров</t>
+  </si>
+  <si>
+    <t>Петрович</t>
+  </si>
+  <si>
+    <t>ул. Гагарина</t>
+  </si>
+  <si>
+    <t>Петрова</t>
+  </si>
+  <si>
+    <t>Ольга</t>
+  </si>
+  <si>
+    <t>Сидорова</t>
+  </si>
+  <si>
+    <t>Сергеевна</t>
+  </si>
+  <si>
+    <t>Сидоров</t>
+  </si>
+  <si>
+    <t>Сергей</t>
+  </si>
+  <si>
+    <t>Олегович</t>
+  </si>
+  <si>
+    <t>Козлов</t>
+  </si>
+  <si>
+    <t>Федорович</t>
+  </si>
+  <si>
+    <t>Козлова</t>
+  </si>
+  <si>
+    <t>Вера</t>
+  </si>
+  <si>
+    <t>Аркадьевна</t>
+  </si>
+  <si>
+    <t>Иваненко</t>
+  </si>
+  <si>
+    <t>Анна</t>
+  </si>
+  <si>
+    <t>Павловна</t>
+  </si>
+  <si>
+    <t>Павел</t>
+  </si>
+  <si>
+    <t>Александрович</t>
+  </si>
+  <si>
+    <t>Попов</t>
+  </si>
+  <si>
+    <t>Алексей</t>
+  </si>
+  <si>
+    <t>Николаевич</t>
+  </si>
+  <si>
+    <t>Попова</t>
+  </si>
+  <si>
+    <t>Екатерина</t>
+  </si>
+  <si>
+    <t>Игоревна</t>
+  </si>
+  <si>
+    <t>Елена</t>
+  </si>
+  <si>
+    <t>Игорь</t>
+  </si>
+  <si>
+    <t>Кузнецов</t>
+  </si>
+  <si>
+    <t>Андрей</t>
+  </si>
+  <si>
+    <t>Алексеевич</t>
+  </si>
+  <si>
+    <t>Кузнецова</t>
+  </si>
+  <si>
+    <t>Ангелина</t>
+  </si>
+  <si>
+    <t>Дмитриевна</t>
+  </si>
+  <si>
+    <t>Дмитрий</t>
+  </si>
+  <si>
+    <t>Александр</t>
+  </si>
+  <si>
+    <t>Игоревич</t>
+  </si>
+  <si>
+    <t>Андреевна</t>
+  </si>
+  <si>
+    <t>Евгений</t>
+  </si>
+  <si>
+    <t>Ирина</t>
+  </si>
+  <si>
+    <t>Наталья</t>
+  </si>
+  <si>
+    <t>Артем</t>
+  </si>
+  <si>
+    <t>Виктория</t>
+  </si>
+  <si>
+    <t>Алексеевна</t>
+  </si>
+  <si>
+    <t>Васильевич</t>
+  </si>
+  <si>
+    <t>Николаевна</t>
+  </si>
+  <si>
+    <t>Николай</t>
+  </si>
+  <si>
+    <t>Олеговна</t>
+  </si>
+  <si>
+    <t>Алина</t>
+  </si>
+  <si>
+    <t>Владимирович</t>
+  </si>
+  <si>
+    <t>Илья</t>
+  </si>
+  <si>
+    <t>Дарья</t>
+  </si>
+  <si>
+    <t>Артемовна</t>
+  </si>
+  <si>
+    <t>Максим</t>
+  </si>
+  <si>
+    <t>Михайловна</t>
+  </si>
+  <si>
+    <t>Кирилл</t>
+  </si>
+  <si>
+    <t>Сергеевич</t>
+  </si>
+  <si>
+    <t>Алла</t>
+  </si>
+  <si>
+    <t>Анастасия</t>
+  </si>
+  <si>
+    <t>Павлович</t>
+  </si>
+  <si>
+    <t>Аркадий</t>
+  </si>
+  <si>
+    <t>Татьяна</t>
+  </si>
+  <si>
+    <t>Полина</t>
+  </si>
+  <si>
+    <t>Сидор</t>
+  </si>
+  <si>
+    <t>Сидорович</t>
+  </si>
+  <si>
+    <t>Викторовна</t>
+  </si>
+  <si>
+    <t>Васильевна</t>
+  </si>
+  <si>
+    <t>Александровна</t>
+  </si>
+  <si>
+    <t>Сидоровна</t>
+  </si>
+  <si>
+    <t>Андреевич</t>
+  </si>
+  <si>
+    <t>Олег</t>
+  </si>
+  <si>
+    <t>Владимир</t>
+  </si>
+  <si>
+    <t>Даниил</t>
+  </si>
+  <si>
+    <t>Григорьевич</t>
+  </si>
+  <si>
+    <t>Виктор</t>
+  </si>
+  <si>
+    <t>Даниилович</t>
+  </si>
+  <si>
+    <t>Артемович</t>
+  </si>
+  <si>
+    <t>Михаил</t>
+  </si>
+  <si>
+    <t>Владимировна</t>
+  </si>
+  <si>
+    <t>Евгения</t>
+  </si>
+  <si>
+    <t>Лариса</t>
+  </si>
+  <si>
+    <t>Вячеславовна</t>
+  </si>
+  <si>
+    <t>Вячеслав</t>
+  </si>
+  <si>
+    <t>RepresentativePhone</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Староград</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Новомир</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Центральный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Первомайск</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Новосвет</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Родники</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесное</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Сокольники</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Южный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Славянск</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Прогресс</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Переходный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полюс</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Заря</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Северный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Мираж</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Восход</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Перспектива</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лунный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Уютный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Вечерний</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Заречный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Стрельник</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Топаз</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Мистерия</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Поднебесный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Сиреневый</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Ольховый</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Луговой</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Луна</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Городской</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярник</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Пламя</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Озерный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Зеленоград</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесной</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Мирный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Весна</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Радуга</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярик</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Сияние</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Путь</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Волна</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Паллада</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Горизонт</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Великий</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лужок</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Весенний</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Парковый</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Чистый</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Радужный</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесное Озеро</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный Луч</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Вечерний Бриз</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечное Зарево</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Уютный Угол</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лунный Аметист</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездная Симфония</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечный Каскад</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярное Сияние</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Летний Ветер</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездное Мерцание</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Весенний Полет</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Радужный Рай</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездная Гармония</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесное Пение</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечная долина</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный Свет</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Вечерний Звонок</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездная Линия</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный Взгляд</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 39</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Радужный Парк</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесное Оживление</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 42</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечная Гавань</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 43</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный Свет</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярная Сказка</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 46</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Уютный Луч</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 47</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный Город</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 48</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный Рай</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 49</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лунное Зеркало</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечное Поле</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 51</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Вечернее Сияние</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 52</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярная Тишина</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 53</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездная Долина</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 54</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесной Оскол</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> д. 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечный Бриз</t>
+  </si>
+  <si>
+    <t>1.</t>
+  </si>
+  <si>
+    <t>2.</t>
+  </si>
+  <si>
+    <t>3.</t>
+  </si>
+  <si>
+    <t>4.</t>
+  </si>
+  <si>
+    <t>5.</t>
+  </si>
+  <si>
+    <t>6.</t>
+  </si>
+  <si>
+    <t>7.</t>
+  </si>
+  <si>
+    <t>8.</t>
+  </si>
+  <si>
+    <t>9.</t>
+  </si>
+  <si>
+    <t>10.</t>
+  </si>
+  <si>
+    <t>пр. Победы</t>
+  </si>
+  <si>
+    <t>пр. Ленинградский</t>
+  </si>
+  <si>
+    <t>ул. Мира</t>
+  </si>
+  <si>
+    <t>ул. Советская</t>
+  </si>
+  <si>
+    <t>пр. Курганский</t>
+  </si>
+  <si>
+    <t>ул. Строителей</t>
+  </si>
+  <si>
+    <t>пр. Московский</t>
+  </si>
+  <si>
+    <t>ул. Большая</t>
+  </si>
+  <si>
+    <t>пр. Октябрьский</t>
+  </si>
+  <si>
+    <t>ул. Революции</t>
+  </si>
+  <si>
+    <t>пр. Народный</t>
+  </si>
+  <si>
+    <t>ул. Центральная</t>
+  </si>
+  <si>
+    <t>пр. Совхозный</t>
+  </si>
+  <si>
+    <t>ул. Зеленая</t>
+  </si>
+  <si>
+    <t>пр. Дружбы</t>
+  </si>
+  <si>
+    <t>ул. Солнечная</t>
+  </si>
+  <si>
+    <t>пр. Заречный</t>
+  </si>
+  <si>
+    <t>ул. Набережная</t>
+  </si>
+  <si>
+    <t>пр. Лесной</t>
+  </si>
+  <si>
+    <t>ул. Полярная</t>
+  </si>
+  <si>
+    <t>пр. Восточный</t>
+  </si>
+  <si>
+    <t>ул. Загородная</t>
+  </si>
+  <si>
+    <t>пр. Степной</t>
+  </si>
+  <si>
+    <t>ул. Октябрская</t>
+  </si>
+  <si>
+    <t>пр. Строительный</t>
+  </si>
+  <si>
+    <t>ул. Парковая</t>
+  </si>
+  <si>
+    <t>пр. Кооперативный</t>
+  </si>
+  <si>
+    <t>ул. Садовая</t>
+  </si>
+  <si>
+    <t>пр. Цветочный</t>
+  </si>
+  <si>
+    <t>ул. Речная</t>
+  </si>
+  <si>
+    <t>пр. Горный</t>
+  </si>
+  <si>
+    <t>ул. Лесная</t>
+  </si>
+  <si>
+    <t>пр. Новый</t>
+  </si>
+  <si>
+    <t>ул. Заводская</t>
+  </si>
+  <si>
+    <t>пр. Луговой</t>
+  </si>
+  <si>
+    <t>ул. Озерная</t>
+  </si>
+  <si>
+    <t>пр. Солнечный</t>
+  </si>
+  <si>
+    <t>ул. Кирова</t>
+  </si>
+  <si>
+    <t>пр. Речной</t>
+  </si>
+  <si>
+    <t>ул. Вокзальная</t>
+  </si>
+  <si>
+    <t>пр. Линейный</t>
+  </si>
+  <si>
+    <t>ул. Красная</t>
+  </si>
+  <si>
+    <t>пр. Зеленый</t>
+  </si>
+  <si>
+    <t>пр. Советский</t>
+  </si>
+  <si>
+    <t>ул. Первомайская</t>
+  </si>
+  <si>
+    <t>пр. Молодежный</t>
+  </si>
+  <si>
+    <t>ул. Новая</t>
+  </si>
+  <si>
+    <t>пр. Олимпийский</t>
+  </si>
+  <si>
+    <t>ул. Южная</t>
+  </si>
+  <si>
+    <t>пр. Набережный</t>
+  </si>
+  <si>
+    <t>пр. Курортный</t>
+  </si>
+  <si>
+    <t>ул. Главная</t>
+  </si>
+  <si>
+    <t>ул. Ленинская</t>
+  </si>
+  <si>
+    <t>пр. Крупный</t>
+  </si>
+  <si>
+    <t>пр. Южный</t>
+  </si>
+  <si>
+    <t>ул. Луговая</t>
+  </si>
+  <si>
+    <t>ул. Цветочная</t>
+  </si>
+  <si>
+    <t>пр. Весенний</t>
+  </si>
+  <si>
+    <t>ул. Сиреневая</t>
+  </si>
+  <si>
+    <t>пр. Звездный</t>
+  </si>
+  <si>
+    <t>ул. Лучевая</t>
+  </si>
+  <si>
+    <t>ул. Ливневая</t>
+  </si>
+  <si>
+    <t>пр. Летний</t>
+  </si>
+  <si>
+    <t>ул. Луночка</t>
+  </si>
+  <si>
+    <t>пр. Зарница</t>
+  </si>
+  <si>
+    <t>ул. Лесопарковая</t>
+  </si>
+  <si>
+    <t>пр. Центральный</t>
+  </si>
+  <si>
+    <t>ул. Звездная</t>
+  </si>
+  <si>
+    <t>пр. Радужный</t>
+  </si>
+  <si>
+    <t>ул. Весенняя</t>
+  </si>
+  <si>
+    <t>пр. Лунный</t>
+  </si>
+  <si>
+    <t>пр. Светлый</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Староград, ул. Ленина,  д. 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Новомир, пр. Победы,  д. 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечный, ул. Гагарина,  д. 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Центральный, ул. Пушкина,  д. 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Первомайск, пр. Ленинградский,  д. 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Новосвет, ул. Мира,  д. 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный, ул. Советская,  д. 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Родники, пр. Курганский,  д. 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесное, ул. Строителей,  д. 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Сокольники, пр. Московский,  д. 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Южный, ул. Большая,  д. 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Славянск, пр. Октябрьский,  д. 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Прогресс, ул. Революции,  д. 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Переходный, пр. Народный,  д. 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полюс, ул. Центральная,  д. 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Заря, пр. Совхозный,  д. 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Северный, ул. Зеленая,  д. 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Мираж, пр. Дружбы,  д. 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Восход, ул. Солнечная,  д. 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Перспектива, пр. Заречный,  д. 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лунный, ул. Набережная,  д. 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Уютный, пр. Лесной,  д. 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Вечерний, ул. Полярная,  д. 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Заречный, пр. Восточный,  д. 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Стрельник, ул. Загородная,  д. 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Топаз, пр. Степной,  д. 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Мистерия, ул. Октябрская,  д. 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Поднебесный, пр. Строительный,  д. 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Сиреневый, ул. Парковая,  д. 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Ольховый, пр. Кооперативный,  д. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный, ул. Садовая,  д. 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный, пр. Цветочный,  д. 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Вечерний, ул. Речная,  д. 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Луговой, пр. Горный,  д. 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Родники, ул. Лесная,  д. 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Восход, пр. Новый,  д. 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечный, ул. Заводская,  д. 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Перспектива, пр. Луговой,  д. 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Заречный, ул. Озерная,  д. 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Заря, пр. Солнечный,  д. 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Луна, ул. Кирова,  д. 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Городской, пр. Речной,  д. 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярник, ул. Вокзальная,  д. 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Пламя, пр. Линейный,  д. 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Озерный, ул. Красная,  д. 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Зеленоград, пр. Зеленый,  д. 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесной, ул. Центральная,  д. 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Мирный, пр. Советский,  д. 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Весна, ул. Первомайская,  д. 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Радуга, пр. Молодежный,  д. 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярик, ул. Новая,  д. 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Сияние, пр. Олимпийский,  д. 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Путь, ул. Южная,  д. 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Волна, пр. Набережный,  д. 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Паллада, ул. Строителей,  д. 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Горизонт, пр. Курортный,  д. 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Великий, ул. Главная,  д. 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лужок, пр. Строительный,  д. 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Весенний, ул. Ленинская,  д. 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Парковый, пр. Крупный,  д. 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Чистый, ул. Советская,  д. 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Радужный, пр. Восточный,  д. 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный, ул. Зеленая,  д. 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесное Озеро, пр. Южный,  д. 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный Луч, ул. Центральная,  д. 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Зеленоград, пр. Солнечный,  д. 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Вечерний Бриз, ул. Лесная,  д. 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечное Зарево, пр. Заречный,  д. 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Уютный Угол, ул. Вокзальная,  д. 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лунный Аметист, пр. Лесной,  д. 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездная Симфония, ул. Полярная,  д. 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечный Каскад, пр. Горный,  д. 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярное Сияние, ул. Набережная,  д. 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Летний Ветер, пр. Совхозный,  д. 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездное Мерцание, ул. Речная,  д. 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Весенний Полет, пр. Молодежный,  д. 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Уютный Угол, ул. Луговая,  д. 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Радужный Рай, пр. Октябрьский,  д. 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездная Гармония, ул. Цветочная,  д. 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесное Пение, пр. Весенний,  д. 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечная долина, ул. Сиреневая,  д. 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный Свет, пр. Звездный,  д. 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Вечерний Звонок, ул. Лучевая,  д. 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездная Линия, пр. Лесной,  д. 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный Взгляд, ул. Ливневая,  д. 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Радужный Парк, пр. Летний,  д. 39</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Лесное Оживление, ул. Озерная,  д. 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Солнечная Гавань, пр. Зеленый,  д. 42</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный Свет, ул. Луночка,  д. 43</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярная Сказка, пр. Зарница,  д. 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Уютный Луч, ул. Солнечная,  д. 46</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Звездный Город, пр. Весенний,  д. 47</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Полярный Рай, ул. Лесопарковая,  д. 48</t>
+  </si>
+  <si>
+    <t>Г-101</t>
+  </si>
+  <si>
+    <t>У-202</t>
+  </si>
+  <si>
+    <t>Г-303</t>
+  </si>
+  <si>
+    <t>С-404</t>
+  </si>
+  <si>
+    <t>К-505</t>
+  </si>
+  <si>
+    <t>Р-606</t>
+  </si>
+  <si>
+    <t>Б-707</t>
+  </si>
+  <si>
+    <t>ГС-808</t>
+  </si>
+  <si>
+    <t>Э-909</t>
+  </si>
+  <si>
+    <t>Т-1010</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,19 +1473,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF252831"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -229,7 +1501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -240,7 +1512,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -256,6 +1539,59 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>224790</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EFED9D8-A3F8-4A3C-BA79-F116CD4C0536}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="7810500"/>
+          <a:ext cx="209550" cy="209550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -810,307 +2146,530 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A70EFCE-2A2C-4B7B-86CF-86AEAB418448}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="5" max="6" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3">
         <v>303</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3">
         <v>304</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>305</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E4" s="3">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="3">
         <v>306</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E5" s="3">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3">
         <v>307</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="3">
         <v>308</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E7" s="3">
+        <v>6</v>
+      </c>
+      <c r="F7" s="3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="3">
         <v>309</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E8" s="3">
+        <v>7</v>
+      </c>
+      <c r="F8" s="3">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="3">
         <v>310</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E9" s="3">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="3">
         <v>311</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E10" s="3">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="3">
         <v>312</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E11" s="3">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="3">
         <v>313</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E12" s="3">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="3">
         <v>314</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E13" s="3">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="3">
         <v>315</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E14" s="3">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="3">
         <v>316</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E15" s="3">
+        <v>14</v>
+      </c>
+      <c r="F15" s="3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="3">
         <v>317</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E16" s="3">
+        <v>15</v>
+      </c>
+      <c r="F16" s="3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="3">
         <v>318</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E17" s="3">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="3">
         <v>319</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E18" s="3">
+        <v>17</v>
+      </c>
+      <c r="F18" s="3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="3">
         <v>320</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E19" s="3">
+        <v>18</v>
+      </c>
+      <c r="F19" s="3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="3">
         <v>321</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E20" s="3">
+        <v>19</v>
+      </c>
+      <c r="F20" s="3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="3">
         <v>322</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E21" s="3">
+        <v>20</v>
+      </c>
+      <c r="F21" s="3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="3">
         <v>323</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E22" s="3">
+        <v>21</v>
+      </c>
+      <c r="F22" s="3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="3">
         <v>324</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E23" s="3">
+        <v>22</v>
+      </c>
+      <c r="F23" s="3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="3">
         <v>325</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E24" s="3">
+        <v>23</v>
+      </c>
+      <c r="F24" s="3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="3">
         <v>326</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E25" s="3">
+        <v>24</v>
+      </c>
+      <c r="F25" s="3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="3">
         <v>327</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E26" s="3">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="3">
         <v>328</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E27" s="3">
+        <v>26</v>
+      </c>
+      <c r="F27" s="3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="3">
         <v>329</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E28" s="3">
+        <v>27</v>
+      </c>
+      <c r="F28" s="3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="3">
         <v>330</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E29" s="3">
+        <v>28</v>
+      </c>
+      <c r="F29" s="3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="3">
         <v>331</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E30" s="3">
+        <v>29</v>
+      </c>
+      <c r="F30" s="3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="3">
         <v>332</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E31" s="3">
+        <v>30</v>
+      </c>
+      <c r="F31" s="3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="3">
         <v>333</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E32" s="3">
+        <v>31</v>
+      </c>
+      <c r="F32" s="3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="3">
         <v>334</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E33" s="3">
+        <v>32</v>
+      </c>
+      <c r="F33" s="3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="3">
         <v>335</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E34" s="3">
+        <v>33</v>
+      </c>
+      <c r="F34" s="3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>35</v>
       </c>
       <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E35" s="3">
+        <v>35</v>
+      </c>
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>36</v>
       </c>
       <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E36" s="3">
+        <v>36</v>
+      </c>
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>37</v>
       </c>
       <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E37" s="3">
+        <v>37</v>
+      </c>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>38</v>
       </c>
       <c r="B38" s="3">
+        <v>309</v>
+      </c>
+      <c r="E38" s="3">
+        <v>38</v>
+      </c>
+      <c r="F38" s="3">
         <v>309</v>
       </c>
     </row>
@@ -1140,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1148,7 +2707,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1157,56 +2716,4592 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA84800-91FB-45F7-9141-3174C2797394}">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FB3ECD-8972-448A-9E6E-0133980551F6}">
+  <dimension ref="A1:R95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="7">
+        <v>79997776655</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="H2" s="6">
+        <v>36270</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="7">
+        <v>79992223311</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="H3" s="6">
+        <v>36753</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="1">
+        <v>79993332244</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1">
+        <v>5</v>
+      </c>
+      <c r="O3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H4" s="6">
+        <v>37169</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="1">
+        <v>79992221155</v>
+      </c>
+      <c r="M4" s="1">
+        <v>2</v>
+      </c>
+      <c r="N4" s="1">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="7">
+        <v>79995556677</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="H5" s="6">
+        <v>36719</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="1">
+        <v>79996667788</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>7</v>
+      </c>
+      <c r="O5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="7">
+        <v>79998887766</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H6" s="6">
+        <v>36185</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="1">
+        <v>79994445566</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="7">
+        <v>79991112233</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="H7" s="6">
+        <v>37225</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" s="1">
+        <v>79992223344</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2</v>
+      </c>
+      <c r="N7" s="1">
+        <v>9</v>
+      </c>
+      <c r="O7" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="7">
+        <v>79993334455</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H8" s="6">
+        <v>36664</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="1">
+        <v>79995556677</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
+        <v>4</v>
+      </c>
+      <c r="O8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="7">
+        <v>79997778899</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="H9" s="6">
+        <v>37104</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="1">
+        <v>79998889900</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1">
+        <v>6</v>
+      </c>
+      <c r="O9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="7">
+        <v>79992223344</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H10" s="6">
+        <v>36597</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M10" s="1">
+        <v>2</v>
+      </c>
+      <c r="N10" s="1">
+        <v>10</v>
+      </c>
+      <c r="O10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="7">
+        <v>79996665544</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="H11" s="6">
+        <v>37079</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L11" s="1">
+        <v>79994443322</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>8</v>
+      </c>
+      <c r="O11" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="7">
+        <v>79992221155</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="H12" s="6">
+        <v>36855</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L12" s="1">
+        <v>79991114433</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>2</v>
+      </c>
+      <c r="O12" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="7">
+        <v>79997776655</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="H13" s="6">
+        <v>36413</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="1">
+        <v>79998882211</v>
+      </c>
+      <c r="M13" s="1">
+        <v>2</v>
+      </c>
+      <c r="N13" s="1">
+        <v>7</v>
+      </c>
+      <c r="O13" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="7">
+        <v>79994445566</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="H14" s="6">
+        <v>36968</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="1">
+        <v>79993337788</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="7">
+        <v>79992223311</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H15" s="6">
+        <v>36732</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L15" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>3</v>
+      </c>
+      <c r="O15" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="H16" s="6">
+        <v>36932</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" s="1">
+        <v>79995558877</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>9</v>
+      </c>
+      <c r="O16" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="7">
+        <v>79993334455</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="H17" s="6">
+        <v>36679</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="1">
+        <v>79992224455</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2</v>
+      </c>
+      <c r="N17" s="1">
+        <v>10</v>
+      </c>
+      <c r="O17" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="7">
+        <v>79998887766</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="H18" s="6">
+        <v>36448</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="1">
+        <v>79997774411</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1">
+        <v>4</v>
+      </c>
+      <c r="O18" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="7">
+        <v>79992223344</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H19" s="6">
+        <v>36880</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1">
+        <v>8</v>
+      </c>
+      <c r="O19" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="7">
+        <v>79996665544</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="H20" s="6">
+        <v>36623</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="1">
+        <v>79994443322</v>
+      </c>
+      <c r="M20" s="1">
+        <v>2</v>
+      </c>
+      <c r="N20" s="1">
+        <v>5</v>
+      </c>
+      <c r="O20" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="7">
+        <v>79997778899</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="H21" s="6">
+        <v>37110</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L21" s="1">
+        <v>79998889900</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1">
+        <v>6</v>
+      </c>
+      <c r="O21" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="7">
+        <v>79997776655</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="H22" s="6">
+        <v>36903</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" s="1">
+        <v>79996665544</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H23" s="6">
+        <v>36860</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L23" s="1">
+        <v>79995556677</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2</v>
+      </c>
+      <c r="N23" s="1">
+        <v>3</v>
+      </c>
+      <c r="O23" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="7">
+        <v>79992221155</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="H24" s="6">
+        <v>36794</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L24" s="1">
+        <v>79993332244</v>
+      </c>
+      <c r="M24" s="1">
+        <v>1</v>
+      </c>
+      <c r="N24" s="1">
+        <v>2</v>
+      </c>
+      <c r="O24" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="7">
+        <v>79991112233</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="H25" s="6">
+        <v>37194</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L25" s="1">
+        <v>79992223344</v>
+      </c>
+      <c r="M25" s="1">
+        <v>1</v>
+      </c>
+      <c r="N25" s="1">
+        <v>9</v>
+      </c>
+      <c r="O25" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="7">
+        <v>79998887766</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="H26" s="6">
+        <v>36326</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L26" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M26" s="1">
+        <v>2</v>
+      </c>
+      <c r="N26" s="1">
+        <v>7</v>
+      </c>
+      <c r="O26" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="7">
+        <v>79992223311</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H27" s="6">
+        <v>36610</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L27" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M27" s="1">
+        <v>1</v>
+      </c>
+      <c r="N27" s="1">
+        <v>10</v>
+      </c>
+      <c r="O27" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="7">
+        <v>79994445566</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H28" s="6">
+        <v>36999</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L28" s="1">
+        <v>79993337788</v>
+      </c>
+      <c r="M28" s="1">
+        <v>1</v>
+      </c>
+      <c r="N28" s="1">
+        <v>8</v>
+      </c>
+      <c r="O28" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="7">
+        <v>79992221155</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="H29" s="6">
+        <v>36855</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L29" s="1">
+        <v>79991114433</v>
+      </c>
+      <c r="M29" s="1">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1">
+        <v>4</v>
+      </c>
+      <c r="O29" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" s="7">
+        <v>79997776655</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="H30" s="6">
+        <v>36413</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30" s="1">
+        <v>79998882211</v>
+      </c>
+      <c r="M30" s="1">
+        <v>2</v>
+      </c>
+      <c r="N30" s="1">
+        <v>6</v>
+      </c>
+      <c r="O30" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="H31" s="6">
+        <v>37077</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L31" s="1">
+        <v>79992221155</v>
+      </c>
+      <c r="M31" s="1">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1">
+        <v>5</v>
+      </c>
+      <c r="O31" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="7">
+        <v>79991234567</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="H32" s="6">
+        <v>36295</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L32" s="1">
+        <v>79998887766</v>
+      </c>
+      <c r="M32" s="1">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" s="7">
+        <v>79997776655</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="H33" s="6">
+        <v>36576</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L33" s="1">
+        <v>79994444555</v>
+      </c>
+      <c r="M33" s="1">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1">
+        <v>3</v>
+      </c>
+      <c r="O33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="7">
+        <v>79996677744</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="H34" s="6">
+        <v>37082</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L34" s="1">
+        <v>79995556644</v>
+      </c>
+      <c r="M34" s="1">
+        <v>2</v>
+      </c>
+      <c r="N34" s="1">
+        <v>2</v>
+      </c>
+      <c r="O34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="7">
+        <v>79992223311</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="H35" s="6">
+        <v>36885</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L35" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M35" s="1">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1">
+        <v>9</v>
+      </c>
+      <c r="O35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H36" s="6">
+        <v>37376</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L36" s="1">
+        <v>79993332211</v>
+      </c>
+      <c r="M36" s="1">
+        <v>2</v>
+      </c>
+      <c r="N36" s="1">
+        <v>7</v>
+      </c>
+      <c r="O36" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="7">
+        <v>79995556677</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H37" s="6">
+        <v>36800</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L37" s="1">
+        <v>79998889900</v>
+      </c>
+      <c r="M37" s="1">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1">
+        <v>10</v>
+      </c>
+      <c r="O37" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="7">
+        <v>79991112233</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H38" s="6">
+        <v>36968</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L38" s="1">
+        <v>79992223344</v>
+      </c>
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1">
+        <v>8</v>
+      </c>
+      <c r="O38" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="B39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" s="7">
+        <v>79997778899</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H39" s="6">
+        <v>36469</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L39" s="1">
+        <v>79996665544</v>
+      </c>
+      <c r="M39" s="1">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1">
+        <v>1</v>
+      </c>
+      <c r="O39" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" s="7">
+        <v>79998887766</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="H40" s="6">
+        <v>36689</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="1">
+        <v>79995554433</v>
+      </c>
+      <c r="M40" s="1">
+        <v>2</v>
+      </c>
+      <c r="N40" s="1">
+        <v>4</v>
+      </c>
+      <c r="O40" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="H41" s="6">
+        <v>37110</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L41" s="1">
+        <v>79997776655</v>
+      </c>
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+      <c r="N41" s="1">
+        <v>6</v>
+      </c>
+      <c r="O41" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="7">
+        <v>79991234567</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H42" s="6">
+        <v>36295</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L42" s="1">
+        <v>79998887766</v>
+      </c>
+      <c r="M42" s="1">
+        <v>1</v>
+      </c>
+      <c r="N42" s="1">
+        <v>5</v>
+      </c>
+      <c r="O42" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="7">
+        <v>79997776655</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="H43" s="6">
+        <v>36576</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43" s="1">
+        <v>79994444555</v>
+      </c>
+      <c r="M43" s="1">
+        <v>1</v>
+      </c>
+      <c r="N43" s="1">
+        <v>3</v>
+      </c>
+      <c r="O43" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" s="7">
+        <v>79996677744</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H44" s="6">
+        <v>37082</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L44" s="1">
+        <v>79995556644</v>
+      </c>
+      <c r="M44" s="1">
+        <v>2</v>
+      </c>
+      <c r="N44" s="1">
+        <v>7</v>
+      </c>
+      <c r="O44" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="7">
+        <v>79992223311</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="H45" s="6">
+        <v>36885</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L45" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M45" s="1">
+        <v>1</v>
+      </c>
+      <c r="N45" s="1">
+        <v>2</v>
+      </c>
+      <c r="O45" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H46" s="6">
+        <v>37376</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L46" s="1">
+        <v>79993332211</v>
+      </c>
+      <c r="M46" s="1">
+        <v>2</v>
+      </c>
+      <c r="N46" s="1">
+        <v>9</v>
+      </c>
+      <c r="O46" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="7">
+        <v>79995556677</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="H47" s="6">
+        <v>36800</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L47" s="1">
+        <v>79998889900</v>
+      </c>
+      <c r="M47" s="1">
+        <v>1</v>
+      </c>
+      <c r="N47" s="1">
+        <v>10</v>
+      </c>
+      <c r="O47" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" s="7">
+        <v>79991112233</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="H48" s="6">
+        <v>36968</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L48" s="1">
+        <v>79992223344</v>
+      </c>
+      <c r="M48" s="1">
+        <v>1</v>
+      </c>
+      <c r="N48" s="1">
+        <v>8</v>
+      </c>
+      <c r="O48" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E49" s="7">
+        <v>79997778899</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="H49" s="6">
+        <v>36469</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L49" s="1">
+        <v>79996665544</v>
+      </c>
+      <c r="M49" s="1">
+        <v>1</v>
+      </c>
+      <c r="N49" s="1">
+        <v>4</v>
+      </c>
+      <c r="O49" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E50" s="7">
+        <v>79998887766</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H50" s="6">
+        <v>36689</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="1">
+        <v>79995554433</v>
+      </c>
+      <c r="M50" s="1">
+        <v>2</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1</v>
+      </c>
+      <c r="O50" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E51" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H51" s="6">
+        <v>37110</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L51" s="1">
+        <v>79997776655</v>
+      </c>
+      <c r="M51" s="1">
+        <v>1</v>
+      </c>
+      <c r="N51" s="1">
+        <v>5</v>
+      </c>
+      <c r="O51" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E52" s="7">
+        <v>79991234567</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H52" s="6">
+        <v>36295</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52" s="1">
+        <v>79998887766</v>
+      </c>
+      <c r="M52" s="1">
+        <v>1</v>
+      </c>
+      <c r="N52" s="1">
+        <v>6</v>
+      </c>
+      <c r="O52" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="7">
+        <v>79997776655</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H53" s="6">
+        <v>36576</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L53" s="1">
+        <v>79994444555</v>
+      </c>
+      <c r="M53" s="1">
+        <v>1</v>
+      </c>
+      <c r="N53" s="1">
+        <v>3</v>
+      </c>
+      <c r="O53" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E54" s="7">
+        <v>79996677744</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H54" s="6">
+        <v>37082</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L54" s="1">
+        <v>79995556644</v>
+      </c>
+      <c r="M54" s="1">
+        <v>2</v>
+      </c>
+      <c r="N54" s="1">
+        <v>2</v>
+      </c>
+      <c r="O54" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E55" s="7">
+        <v>79992223311</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H55" s="6">
+        <v>36885</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L55" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M55" s="1">
+        <v>1</v>
+      </c>
+      <c r="N55" s="1">
+        <v>7</v>
+      </c>
+      <c r="O55" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H56" s="6">
+        <v>37376</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L56" s="1">
+        <v>79993332211</v>
+      </c>
+      <c r="M56" s="1">
+        <v>2</v>
+      </c>
+      <c r="N56" s="1">
+        <v>9</v>
+      </c>
+      <c r="O56" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57" s="7">
+        <v>79995556677</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H57" s="6">
+        <v>36800</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L57" s="1">
+        <v>79998889900</v>
+      </c>
+      <c r="M57" s="1">
+        <v>1</v>
+      </c>
+      <c r="N57" s="1">
+        <v>10</v>
+      </c>
+      <c r="O57" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" s="7">
+        <v>79991112233</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H58" s="6">
+        <v>36968</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L58" s="1">
+        <v>79992223344</v>
+      </c>
+      <c r="M58" s="1">
+        <v>1</v>
+      </c>
+      <c r="N58" s="1">
+        <v>8</v>
+      </c>
+      <c r="O58" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" s="7">
+        <v>79997778899</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H59" s="6">
+        <v>36469</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L59" s="1">
+        <v>79996665544</v>
+      </c>
+      <c r="M59" s="1">
+        <v>1</v>
+      </c>
+      <c r="N59" s="1">
+        <v>4</v>
+      </c>
+      <c r="O59" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" s="7">
+        <v>79998887766</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H60" s="6">
+        <v>36689</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="1">
+        <v>79995554433</v>
+      </c>
+      <c r="M60" s="1">
+        <v>2</v>
+      </c>
+      <c r="N60" s="1">
+        <v>1</v>
+      </c>
+      <c r="O60" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="H61" s="6">
+        <v>37110</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L61" s="1">
+        <v>79997776655</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1</v>
+      </c>
+      <c r="N61" s="1">
+        <v>5</v>
+      </c>
+      <c r="O61" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E62" s="7">
+        <v>79991234567</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="H62" s="6">
+        <v>36295</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L62" s="1">
+        <v>79998887766</v>
+      </c>
+      <c r="M62" s="1">
+        <v>1</v>
+      </c>
+      <c r="N62" s="1">
+        <v>3</v>
+      </c>
+      <c r="O62" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" s="7">
+        <v>79997776655</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="H63" s="6">
+        <v>36576</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L63" s="1">
+        <v>79994444555</v>
+      </c>
+      <c r="M63" s="1">
+        <v>1</v>
+      </c>
+      <c r="N63" s="1">
+        <v>6</v>
+      </c>
+      <c r="O63" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E64" s="7">
+        <v>79996677744</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="H64" s="6">
+        <v>37082</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L64" s="1">
+        <v>79995556644</v>
+      </c>
+      <c r="M64" s="1">
+        <v>2</v>
+      </c>
+      <c r="N64" s="1">
+        <v>7</v>
+      </c>
+      <c r="O64" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E65" s="7">
+        <v>79992223311</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H65" s="6">
+        <v>36885</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L65" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M65" s="1">
+        <v>1</v>
+      </c>
+      <c r="N65" s="1">
+        <v>2</v>
+      </c>
+      <c r="O65" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H66" s="6">
+        <v>37376</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L66" s="1">
+        <v>79993332211</v>
+      </c>
+      <c r="M66" s="1">
+        <v>2</v>
+      </c>
+      <c r="N66" s="1">
+        <v>9</v>
+      </c>
+      <c r="O66" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" s="7">
+        <v>79995556677</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H67" s="6">
+        <v>36800</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L67" s="1">
+        <v>79998889900</v>
+      </c>
+      <c r="M67" s="1">
+        <v>1</v>
+      </c>
+      <c r="N67" s="1">
+        <v>10</v>
+      </c>
+      <c r="O67" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="7">
+        <v>79991112233</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H68" s="6">
+        <v>36968</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L68" s="1">
+        <v>79992223344</v>
+      </c>
+      <c r="M68" s="1">
+        <v>1</v>
+      </c>
+      <c r="N68" s="1">
+        <v>8</v>
+      </c>
+      <c r="O68" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E69" s="7">
+        <v>79997778899</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="H69" s="6">
+        <v>36469</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L69" s="1">
+        <v>79996665544</v>
+      </c>
+      <c r="M69" s="1">
+        <v>1</v>
+      </c>
+      <c r="N69" s="1">
+        <v>4</v>
+      </c>
+      <c r="O69" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E70" s="7">
+        <v>79998887766</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="H70" s="6">
+        <v>36689</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L70" s="1">
+        <v>79995554433</v>
+      </c>
+      <c r="M70" s="1">
+        <v>2</v>
+      </c>
+      <c r="N70" s="1">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="7">
+        <v>79994443322</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H71" s="6">
+        <v>37110</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L71" s="1">
+        <v>79997776655</v>
+      </c>
+      <c r="M71" s="1">
+        <v>1</v>
+      </c>
+      <c r="N71" s="1">
+        <v>6</v>
+      </c>
+      <c r="O71" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E72" s="7">
+        <v>79994446688</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H72" s="6">
+        <v>36750</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L72" s="1">
+        <v>79992223399</v>
+      </c>
+      <c r="M72" s="1">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1">
+        <v>5</v>
+      </c>
+      <c r="O72" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" s="7">
+        <v>79997772233</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="H73" s="6">
+        <v>36950</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L73" s="1">
+        <v>79998885577</v>
+      </c>
+      <c r="M73" s="1">
+        <v>2</v>
+      </c>
+      <c r="N73" s="1">
+        <v>3</v>
+      </c>
+      <c r="O73" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E74" s="7">
+        <v>79995558899</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H74" s="6">
+        <v>36474</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L74" s="1">
+        <v>79996667744</v>
+      </c>
+      <c r="M74" s="1">
+        <v>1</v>
+      </c>
+      <c r="N74" s="1">
+        <v>7</v>
+      </c>
+      <c r="O74" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E75" s="7">
+        <v>79994442211</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H75" s="6">
+        <v>36732</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L75" s="1">
+        <v>79991113322</v>
+      </c>
+      <c r="M75" s="1">
+        <v>2</v>
+      </c>
+      <c r="N75" s="1">
+        <v>2</v>
+      </c>
+      <c r="O75" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E76" s="7">
+        <v>79993331177</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H76" s="6">
+        <v>37330</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L76" s="1">
+        <v>79992226655</v>
+      </c>
+      <c r="M76" s="1">
+        <v>1</v>
+      </c>
+      <c r="N76" s="1">
+        <v>9</v>
+      </c>
+      <c r="O76" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E77" s="7">
+        <v>79991116633</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="H77" s="6">
+        <v>36758</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L77" s="1">
+        <v>79999998877</v>
+      </c>
+      <c r="M77" s="1">
+        <v>2</v>
+      </c>
+      <c r="N77" s="1">
+        <v>10</v>
+      </c>
+      <c r="O77" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E78" s="7">
+        <v>79998888833</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="H78" s="6">
+        <v>37004</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L78" s="1">
+        <v>79993331144</v>
+      </c>
+      <c r="M78" s="1">
+        <v>1</v>
+      </c>
+      <c r="N78" s="1">
+        <v>8</v>
+      </c>
+      <c r="O78" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="7">
+        <v>79992229933</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H79" s="6">
+        <v>36451</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L79" s="1">
+        <v>79994446677</v>
+      </c>
+      <c r="M79" s="1">
+        <v>2</v>
+      </c>
+      <c r="N79" s="1">
+        <v>4</v>
+      </c>
+      <c r="O79" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E80" s="7">
+        <v>79992228811</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H80" s="6">
+        <v>37077</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="1">
+        <v>79993336677</v>
+      </c>
+      <c r="M80" s="1">
+        <v>1</v>
+      </c>
+      <c r="N80" s="1">
+        <v>1</v>
+      </c>
+      <c r="O80" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E81" s="7">
+        <v>79998886611</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H81" s="6">
+        <v>36889</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L81" s="1">
+        <v>79997773322</v>
+      </c>
+      <c r="M81" s="1">
+        <v>2</v>
+      </c>
+      <c r="N81" s="1">
+        <v>5</v>
+      </c>
+      <c r="O81" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E82" s="7">
+        <v>79996662288</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H82" s="6">
+        <v>36959</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L82" s="1">
+        <v>79993339911</v>
+      </c>
+      <c r="M82" s="1">
+        <v>1</v>
+      </c>
+      <c r="N82" s="1">
+        <v>6</v>
+      </c>
+      <c r="O82" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E83" s="7">
+        <v>79995557700</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="H83" s="6">
+        <v>36752</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L83" s="1">
+        <v>79998884455</v>
+      </c>
+      <c r="M83" s="1">
+        <v>2</v>
+      </c>
+      <c r="N83" s="1">
+        <v>2</v>
+      </c>
+      <c r="O83" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E84" s="7">
+        <v>79994447799</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H84" s="6">
+        <v>36921</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L84" s="1">
+        <v>79992222244</v>
+      </c>
+      <c r="M84" s="1">
+        <v>1</v>
+      </c>
+      <c r="N84" s="1">
+        <v>3</v>
+      </c>
+      <c r="O84" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E85" s="7">
+        <v>79991113300</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H85" s="6">
+        <v>36650</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L85" s="1">
+        <v>79998883377</v>
+      </c>
+      <c r="M85" s="1">
+        <v>2</v>
+      </c>
+      <c r="N85" s="1">
+        <v>7</v>
+      </c>
+      <c r="O85" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E86" s="7">
+        <v>79997770022</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H86" s="6">
+        <v>36810</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L86" s="1">
+        <v>79994446699</v>
+      </c>
+      <c r="M86" s="1">
+        <v>1</v>
+      </c>
+      <c r="N86" s="1">
+        <v>9</v>
+      </c>
+      <c r="O86" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E87" s="7">
+        <v>79994441100</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H87" s="6">
+        <v>37125</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L87" s="1">
+        <v>79993337766</v>
+      </c>
+      <c r="M87" s="1">
+        <v>2</v>
+      </c>
+      <c r="N87" s="1">
+        <v>10</v>
+      </c>
+      <c r="O87" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E88" s="7">
+        <v>79992228833</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="H88" s="6">
+        <v>36774</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L88" s="1">
+        <v>79991116655</v>
+      </c>
+      <c r="M88" s="1">
+        <v>1</v>
+      </c>
+      <c r="N88" s="1">
+        <v>8</v>
+      </c>
+      <c r="O88" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E89" s="7">
+        <v>79998883300</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="H89" s="6">
+        <v>36939</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L89" s="1">
+        <v>79992225588</v>
+      </c>
+      <c r="M89" s="1">
+        <v>2</v>
+      </c>
+      <c r="N89" s="1">
+        <v>4</v>
+      </c>
+      <c r="O89" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E90" s="7">
+        <v>79996664400</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="H90" s="6">
+        <v>36636</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L90" s="1">
+        <v>79994448811</v>
+      </c>
+      <c r="M90" s="1">
+        <v>1</v>
+      </c>
+      <c r="N90" s="1">
+        <v>1</v>
+      </c>
+      <c r="O90" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E91" s="7">
+        <v>79995557733</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="H91" s="6">
+        <v>37188</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L91" s="1">
+        <v>79998880022</v>
+      </c>
+      <c r="M91" s="1">
+        <v>2</v>
+      </c>
+      <c r="N91" s="1">
+        <v>5</v>
+      </c>
+      <c r="O91" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E92" s="7">
+        <v>79994445566</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H92" s="6">
+        <v>36540</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L92" s="1">
+        <v>79993332211</v>
+      </c>
+      <c r="M92" s="1">
+        <v>1</v>
+      </c>
+      <c r="N92" s="1">
+        <v>6</v>
+      </c>
+      <c r="O92" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E93" s="7">
+        <v>79991112233</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="H93" s="6">
+        <v>37072</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L93" s="1">
+        <v>79992223344</v>
+      </c>
+      <c r="M93" s="1">
+        <v>2</v>
+      </c>
+      <c r="N93" s="1">
+        <v>3</v>
+      </c>
+      <c r="O93" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="5">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E94" s="7">
+        <v>79998887766</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="H94" s="6">
+        <v>36499</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L94" s="1">
+        <v>79991112233</v>
+      </c>
+      <c r="M94" s="1">
+        <v>1</v>
+      </c>
+      <c r="N94" s="1">
+        <v>7</v>
+      </c>
+      <c r="O94" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E95" s="7">
+        <v>79996665544</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H95" s="6">
+        <v>36727</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L95" s="1">
+        <v>79994443322</v>
+      </c>
+      <c r="M95" s="1">
+        <v>2</v>
+      </c>
+      <c r="N95" s="1">
+        <v>2</v>
+      </c>
+      <c r="O95" s="1">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD781B1-B8D7-4044-89C0-83D3AD1AC099}">
-  <dimension ref="A1:D1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0660ACF4-B723-48AE-8FF5-D2A89F8623AF}">
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -1215,91 +7310,1582 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BAA03BA-F000-4D1A-9132-90877A1E8DB5}">
-  <dimension ref="A1:E1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAEFCF6-14E7-4717-9062-56618BB5238B}">
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>51</v>
+        <v>147</v>
+      </c>
+      <c r="D1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1" t="str">
+        <f>CONCATENATE(C1,", ",A1,", ",B1)</f>
+        <v xml:space="preserve"> г. Староград, ул. Ленина,  д. 10</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" t="str">
+        <f t="shared" ref="E2:E65" si="0">CONCATENATE(C2,", ",A2,", ",B2)</f>
+        <v xml:space="preserve"> г. Новомир, пр. Победы,  д. 25</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="J2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Солнечный, ул. Гагарина,  д. 7</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="J3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Центральный, ул. Пушкина,  д. 15</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Первомайск, пр. Ленинградский,  д. 3</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="J5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Новосвет, ул. Мира,  д. 8</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="J6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Звездный, ул. Советская,  д. 12</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="J7" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Родники, пр. Курганский,  д. 17</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="J8" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Лесное, ул. Строителей,  д. 22</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="J9" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Сокольники, пр. Московский,  д. 30</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="J10" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Южный, ул. Большая,  д. 5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Славянск, пр. Октябрьский,  д. 11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>306</v>
+      </c>
+      <c r="B13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Прогресс, ул. Революции,  д. 20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Переходный, пр. Народный,  д. 13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>308</v>
+      </c>
+      <c r="B15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Полюс, ул. Центральная,  д. 18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Заря, пр. Совхозный,  д. 27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Северный, ул. Зеленая,  д. 9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>311</v>
+      </c>
+      <c r="B18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Мираж, пр. Дружбы,  д. 14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Восход, ул. Солнечная,  д. 6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Перспектива, пр. Заречный,  д. 23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Лунный, ул. Набережная,  д. 4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>315</v>
+      </c>
+      <c r="B22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Уютный, пр. Лесной,  д. 21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>316</v>
+      </c>
+      <c r="B23" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Вечерний, ул. Полярная,  д. 19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>317</v>
+      </c>
+      <c r="B24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Заречный, пр. Восточный,  д. 26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Стрельник, ул. Загородная,  д. 24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" t="s">
+        <v>197</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Топаз, пр. Степной,  д. 29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>320</v>
+      </c>
+      <c r="B27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Мистерия, ул. Октябрская,  д. 28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>321</v>
+      </c>
+      <c r="B28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" t="s">
+        <v>201</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Поднебесный, пр. Строительный,  д. 1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" t="s">
+        <v>203</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Сиреневый, ул. Парковая,  д. 16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" t="s">
+        <v>205</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Ольховый, пр. Кооперативный,  д. 2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>324</v>
+      </c>
+      <c r="B31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Звездный, ул. Садовая,  д. 11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Полярный, пр. Цветочный,  д. 8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Вечерний, ул. Речная,  д. 14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>327</v>
+      </c>
+      <c r="B34" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" t="s">
+        <v>207</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Луговой, пр. Горный,  д. 6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>328</v>
+      </c>
+      <c r="B35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" t="s">
+        <v>161</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Родники, ул. Лесная,  д. 19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Восход, пр. Новый,  д. 25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" t="s">
+        <v>151</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Солнечный, ул. Заводская,  д. 7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Перспектива, пр. Луговой,  д. 12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>332</v>
+      </c>
+      <c r="B39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" t="s">
+        <v>193</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Заречный, ул. Озерная,  д. 22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>333</v>
+      </c>
+      <c r="B40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Заря, пр. Солнечный,  д. 15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>334</v>
+      </c>
+      <c r="B41" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Луна, ул. Кирова,  д. 9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" t="s">
+        <v>202</v>
+      </c>
+      <c r="C42" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Городской, пр. Речной,  д. 16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" t="s">
+        <v>170</v>
+      </c>
+      <c r="C43" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Полярник, ул. Вокзальная,  д. 20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>337</v>
+      </c>
+      <c r="B44" t="s">
+        <v>160</v>
+      </c>
+      <c r="C44" t="s">
+        <v>211</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Пламя, пр. Линейный,  д. 17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>338</v>
+      </c>
+      <c r="B45" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" t="s">
+        <v>212</v>
+      </c>
+      <c r="E45" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Озерный, ул. Красная,  д. 23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>339</v>
+      </c>
+      <c r="B46" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" t="s">
+        <v>213</v>
+      </c>
+      <c r="E46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Зеленоград, пр. Зеленый,  д. 10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>308</v>
+      </c>
+      <c r="B47" t="s">
+        <v>198</v>
+      </c>
+      <c r="C47" t="s">
+        <v>214</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Лесной, ул. Центральная,  д. 28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>340</v>
+      </c>
+      <c r="B48" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Мирный, пр. Советский,  д. 13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>341</v>
+      </c>
+      <c r="B49" t="s">
+        <v>192</v>
+      </c>
+      <c r="C49" t="s">
+        <v>216</v>
+      </c>
+      <c r="E49" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Весна, ул. Первомайская,  д. 26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>342</v>
+      </c>
+      <c r="B50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" t="s">
+        <v>217</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Радуга, пр. Молодежный,  д. 18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>343</v>
+      </c>
+      <c r="B51" t="s">
+        <v>188</v>
+      </c>
+      <c r="C51" t="s">
+        <v>218</v>
+      </c>
+      <c r="E51" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Полярик, ул. Новая,  д. 21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>344</v>
+      </c>
+      <c r="B52" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" t="s">
+        <v>219</v>
+      </c>
+      <c r="E52" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Сияние, пр. Олимпийский,  д. 27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>345</v>
+      </c>
+      <c r="B53" t="s">
+        <v>194</v>
+      </c>
+      <c r="C53" t="s">
+        <v>220</v>
+      </c>
+      <c r="E53" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Путь, ул. Южная,  д. 24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>346</v>
+      </c>
+      <c r="B54" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" t="s">
+        <v>221</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Волна, пр. Набережный,  д. 30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>302</v>
+      </c>
+      <c r="B55" t="s">
+        <v>222</v>
+      </c>
+      <c r="C55" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Паллада, ул. Строителей,  д. 31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>347</v>
+      </c>
+      <c r="B56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C56" t="s">
+        <v>224</v>
+      </c>
+      <c r="E56" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Горизонт, пр. Курортный,  д. 29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>348</v>
+      </c>
+      <c r="B57" t="s">
+        <v>225</v>
+      </c>
+      <c r="C57" t="s">
+        <v>226</v>
+      </c>
+      <c r="E57" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Великий, ул. Главная,  д. 32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>321</v>
+      </c>
+      <c r="B58" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" t="s">
+        <v>228</v>
+      </c>
+      <c r="E58" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Лужок, пр. Строительный,  д. 33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>349</v>
+      </c>
+      <c r="B59" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Весенний, ул. Ленинская,  д. 34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>350</v>
+      </c>
+      <c r="B60" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" t="s">
+        <v>232</v>
+      </c>
+      <c r="E60" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Парковый, пр. Крупный,  д. 35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>300</v>
+      </c>
+      <c r="B61" t="s">
+        <v>146</v>
+      </c>
+      <c r="C61" t="s">
+        <v>233</v>
+      </c>
+      <c r="E61" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Чистый, ул. Советская,  д. 10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>317</v>
+      </c>
+      <c r="B62" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" t="s">
+        <v>234</v>
+      </c>
+      <c r="E62" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Радужный, пр. Восточный,  д. 9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>310</v>
+      </c>
+      <c r="B63" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63" t="s">
+        <v>206</v>
+      </c>
+      <c r="E63" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Полярный, ул. Зеленая,  д. 18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>351</v>
+      </c>
+      <c r="B64" t="s">
+        <v>162</v>
+      </c>
+      <c r="C64" t="s">
+        <v>235</v>
+      </c>
+      <c r="E64" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Лесное Озеро, пр. Южный,  д. 22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>308</v>
+      </c>
+      <c r="B65" t="s">
+        <v>176</v>
+      </c>
+      <c r="C65" t="s">
+        <v>236</v>
+      </c>
+      <c r="E65" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> г. Звездный Луч, ул. Центральная,  д. 27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>333</v>
+      </c>
+      <c r="B66" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" t="s">
+        <v>213</v>
+      </c>
+      <c r="E66" t="str">
+        <f t="shared" ref="E66:E100" si="1">CONCATENATE(C66,", ",A66,", ",B66)</f>
+        <v xml:space="preserve"> г. Зеленоград, пр. Солнечный,  д. 14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>328</v>
+      </c>
+      <c r="B67" t="s">
+        <v>188</v>
+      </c>
+      <c r="C67" t="s">
+        <v>237</v>
+      </c>
+      <c r="E67" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Вечерний Бриз, ул. Лесная,  д. 21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>313</v>
+      </c>
+      <c r="B68" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" t="s">
+        <v>238</v>
+      </c>
+      <c r="E68" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Солнечное Зарево, пр. Заречный,  д. 17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>336</v>
+      </c>
+      <c r="B69" t="s">
+        <v>202</v>
+      </c>
+      <c r="C69" t="s">
+        <v>239</v>
+      </c>
+      <c r="E69" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Уютный Угол, ул. Вокзальная,  д. 16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>315</v>
+      </c>
+      <c r="B70" t="s">
+        <v>184</v>
+      </c>
+      <c r="C70" t="s">
+        <v>240</v>
+      </c>
+      <c r="E70" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Лунный Аметист, пр. Лесной,  д. 23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>316</v>
+      </c>
+      <c r="B71" t="s">
+        <v>198</v>
+      </c>
+      <c r="C71" t="s">
+        <v>241</v>
+      </c>
+      <c r="E71" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Звездная Симфония, ул. Полярная,  д. 28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>327</v>
+      </c>
+      <c r="B72" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" t="s">
+        <v>242</v>
+      </c>
+      <c r="E72" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Солнечный Каскад, пр. Горный,  д. 19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>314</v>
+      </c>
+      <c r="B73" t="s">
+        <v>192</v>
+      </c>
+      <c r="C73" t="s">
+        <v>243</v>
+      </c>
+      <c r="E73" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Полярное Сияние, ул. Набережная,  д. 26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>309</v>
+      </c>
+      <c r="B74" t="s">
+        <v>164</v>
+      </c>
+      <c r="C74" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Летний Ветер, пр. Совхозный,  д. 30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>326</v>
+      </c>
+      <c r="B75" t="s">
+        <v>148</v>
+      </c>
+      <c r="C75" t="s">
+        <v>245</v>
+      </c>
+      <c r="E75" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Звездное Мерцание, ул. Речная,  д. 25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>342</v>
+      </c>
+      <c r="B76" t="s">
+        <v>170</v>
+      </c>
+      <c r="C76" t="s">
+        <v>246</v>
+      </c>
+      <c r="E76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Весенний Полет, пр. Молодежный,  д. 20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>352</v>
+      </c>
+      <c r="B77" t="s">
+        <v>194</v>
+      </c>
+      <c r="C77" t="s">
+        <v>239</v>
+      </c>
+      <c r="E77" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Уютный Угол, ул. Луговая,  д. 24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>305</v>
+      </c>
+      <c r="B78" t="s">
+        <v>222</v>
+      </c>
+      <c r="C78" t="s">
+        <v>247</v>
+      </c>
+      <c r="E78" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Радужный Рай, пр. Октябрьский,  д. 31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>353</v>
+      </c>
+      <c r="B79" t="s">
+        <v>225</v>
+      </c>
+      <c r="C79" t="s">
+        <v>248</v>
+      </c>
+      <c r="E79" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Звездная Гармония, ул. Цветочная,  д. 32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>354</v>
+      </c>
+      <c r="B80" t="s">
+        <v>196</v>
+      </c>
+      <c r="C80" t="s">
+        <v>249</v>
+      </c>
+      <c r="E80" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Лесное Пение, пр. Весенний,  д. 29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>355</v>
+      </c>
+      <c r="B81" t="s">
+        <v>227</v>
+      </c>
+      <c r="C81" t="s">
+        <v>250</v>
+      </c>
+      <c r="E81" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Солнечная долина, ул. Сиреневая,  д. 33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>356</v>
+      </c>
+      <c r="B82" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" t="s">
+        <v>251</v>
+      </c>
+      <c r="E82" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Полярный Свет, пр. Звездный,  д. 35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>357</v>
+      </c>
+      <c r="B83" t="s">
+        <v>252</v>
+      </c>
+      <c r="C83" t="s">
+        <v>253</v>
+      </c>
+      <c r="E83" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Вечерний Звонок, ул. Лучевая,  д. 36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>315</v>
+      </c>
+      <c r="B84" t="s">
+        <v>229</v>
+      </c>
+      <c r="C84" t="s">
+        <v>254</v>
+      </c>
+      <c r="E84" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Звездная Линия, пр. Лесной,  д. 34</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>358</v>
+      </c>
+      <c r="B85" t="s">
+        <v>255</v>
+      </c>
+      <c r="C85" t="s">
+        <v>256</v>
+      </c>
+      <c r="E85" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Полярный Взгляд, ул. Ливневая,  д. 38</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>359</v>
+      </c>
+      <c r="B86" t="s">
+        <v>257</v>
+      </c>
+      <c r="C86" t="s">
+        <v>258</v>
+      </c>
+      <c r="E86" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Радужный Парк, пр. Летний,  д. 39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>332</v>
+      </c>
+      <c r="B87" t="s">
+        <v>259</v>
+      </c>
+      <c r="C87" t="s">
+        <v>260</v>
+      </c>
+      <c r="E87" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Лесное Оживление, ул. Озерная,  д. 40</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>339</v>
+      </c>
+      <c r="B88" t="s">
+        <v>261</v>
+      </c>
+      <c r="C88" t="s">
+        <v>262</v>
+      </c>
+      <c r="E88" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Солнечная Гавань, пр. Зеленый,  д. 42</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" t="s">
+        <v>264</v>
+      </c>
+      <c r="E89" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Звездный Свет, ул. Луночка,  д. 43</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>361</v>
+      </c>
+      <c r="B90" t="s">
+        <v>265</v>
+      </c>
+      <c r="C90" t="s">
+        <v>266</v>
+      </c>
+      <c r="E90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Полярная Сказка, пр. Зарница,  д. 44</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>312</v>
+      </c>
+      <c r="B91" t="s">
+        <v>267</v>
+      </c>
+      <c r="C91" t="s">
+        <v>268</v>
+      </c>
+      <c r="E91" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Уютный Луч, ул. Солнечная,  д. 46</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>354</v>
+      </c>
+      <c r="B92" t="s">
+        <v>269</v>
+      </c>
+      <c r="C92" t="s">
+        <v>270</v>
+      </c>
+      <c r="E92" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Звездный Город, пр. Весенний,  д. 47</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>362</v>
+      </c>
+      <c r="B93" t="s">
+        <v>271</v>
+      </c>
+      <c r="C93" t="s">
+        <v>272</v>
+      </c>
+      <c r="E93" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Полярный Рай, ул. Лесопарковая,  д. 48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>363</v>
+      </c>
+      <c r="B94" t="s">
+        <v>273</v>
+      </c>
+      <c r="C94" t="s">
+        <v>274</v>
+      </c>
+      <c r="E94" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Лунное Зеркало, пр. Центральный,  д. 49</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>364</v>
+      </c>
+      <c r="B95" t="s">
+        <v>275</v>
+      </c>
+      <c r="C95" t="s">
+        <v>276</v>
+      </c>
+      <c r="E95" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Солнечное Поле, ул. Звездная,  д. 50</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>365</v>
+      </c>
+      <c r="B96" t="s">
+        <v>277</v>
+      </c>
+      <c r="C96" t="s">
+        <v>278</v>
+      </c>
+      <c r="E96" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Вечернее Сияние, пр. Радужный,  д. 51</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>366</v>
+      </c>
+      <c r="B97" t="s">
+        <v>279</v>
+      </c>
+      <c r="C97" t="s">
+        <v>280</v>
+      </c>
+      <c r="E97" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Полярная Тишина, ул. Весенняя,  д. 52</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>367</v>
+      </c>
+      <c r="B98" t="s">
+        <v>281</v>
+      </c>
+      <c r="C98" t="s">
+        <v>282</v>
+      </c>
+      <c r="E98" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Звездная Долина, пр. Лунный,  д. 53</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>332</v>
+      </c>
+      <c r="B99" t="s">
+        <v>283</v>
+      </c>
+      <c r="C99" t="s">
+        <v>284</v>
+      </c>
+      <c r="E99" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Лесной Оскол, ул. Озерная,  д. 54</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>368</v>
+      </c>
+      <c r="B100" t="s">
+        <v>285</v>
+      </c>
+      <c r="C100" t="s">
+        <v>286</v>
+      </c>
+      <c r="E100" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> г. Солнечный Бриз, пр. Светлый,  д. 55</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9FB3ECD-8972-448A-9E6E-0133980551F6}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
+  <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>